--- a/e2e/data/catalogs/user-management.xlsx
+++ b/e2e/data/catalogs/user-management.xlsx
@@ -6409,7 +6409,7 @@
         <v>14</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>16</v>
@@ -7397,7 +7397,7 @@
         <v>14</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>80</v>
